--- a/data/Blumenau/Janeiro 2025 - Giassi.xlsx
+++ b/data/Blumenau/Janeiro 2025 - Giassi.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bttom\OneDrive - FURB\Documentos\GitHub\CidadaniaFinanceira\data\Blumenau\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67537C82-2C33-4461-B152-DB8BBEAADDD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -122,6 +128,9 @@
     <t>Feijão Preto</t>
   </si>
   <si>
+    <t>Caldobom</t>
+  </si>
+  <si>
     <t>Manteiga</t>
   </si>
   <si>
@@ -194,6 +203,9 @@
     <t>Parmalat</t>
   </si>
   <si>
+    <t xml:space="preserve">Amanhecer </t>
+  </si>
+  <si>
     <t xml:space="preserve">Tirol </t>
   </si>
   <si>
@@ -204,22 +216,16 @@
   </si>
   <si>
     <t>Janeiro/2025</t>
-  </si>
-  <si>
-    <t>Caldobom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amanhecer </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -835,7 +841,7 @@
         <xdr:cNvPr id="3" name="Imagem 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{440C6053-FEDB-4212-B9E7-E3BDFE1000EA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{440C6053-FEDB-4212-B9E7-E3BDFE1000EA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1119,31 +1125,31 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="10.5703125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="8.7109375" style="4"/>
-    <col min="13" max="13" width="11.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.7109375" style="4"/>
+    <col min="4" max="4" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="10.5546875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8.6640625" style="4"/>
+    <col min="13" max="13" width="11.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="18"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1154,7 +1160,7 @@
       <c r="H1" s="19"/>
       <c r="I1" s="21"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -1165,7 +1171,7 @@
       <c r="H2" s="23"/>
       <c r="I2" s="25"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="22"/>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -1176,7 +1182,7 @@
       <c r="H3" s="23"/>
       <c r="I3" s="25"/>
     </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="27"/>
@@ -1187,7 +1193,7 @@
       <c r="H4" s="27"/>
       <c r="I4" s="29"/>
     </row>
-    <row r="5" spans="1:9" ht="16.5" customHeight="1">
+    <row r="5" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
         <v>0</v>
       </c>
@@ -1199,14 +1205,14 @@
         <v>2</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F5" s="55"/>
       <c r="G5" s="55"/>
       <c r="H5" s="16"/>
       <c r="I5" s="17"/>
     </row>
-    <row r="6" spans="1:9" ht="16.5" customHeight="1">
+    <row r="6" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1229,7 +1235,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
         <v>9</v>
       </c>
@@ -1256,10 +1262,10 @@
       </c>
       <c r="I7" s="56">
         <f>AVERAGE(F8:H8)</f>
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="16.5" customHeight="1">
+        <v>5.1466666666666656</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="37"/>
       <c r="B8" s="39"/>
       <c r="C8" s="39"/>
@@ -1271,14 +1277,14 @@
         <v>6.18</v>
       </c>
       <c r="G8" s="7">
-        <v>4.58</v>
+        <v>3.88</v>
       </c>
       <c r="H8" s="8">
         <v>5.38</v>
       </c>
       <c r="I8" s="57"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="42" t="s">
         <v>16</v>
       </c>
@@ -1308,7 +1314,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16.5" customHeight="1">
+    <row r="10" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="43"/>
       <c r="B10" s="45"/>
       <c r="C10" s="45"/>
@@ -1327,7 +1333,7 @@
       </c>
       <c r="I10" s="61"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
         <v>20</v>
       </c>
@@ -1354,10 +1360,10 @@
       </c>
       <c r="I11" s="56">
         <f>AVERAGE(F12:H12)</f>
-        <v>21.646666666666665</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16.5" customHeight="1">
+        <v>29.98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="37"/>
       <c r="B12" s="39"/>
       <c r="C12" s="39"/>
@@ -1366,17 +1372,17 @@
         <v>15</v>
       </c>
       <c r="F12" s="7">
-        <v>22.98</v>
+        <v>30.98</v>
       </c>
       <c r="G12" s="7">
-        <v>19.98</v>
+        <v>28.98</v>
       </c>
       <c r="H12" s="8">
-        <v>21.98</v>
+        <v>29.98</v>
       </c>
       <c r="I12" s="57"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="42" t="s">
         <v>24</v>
       </c>
@@ -1403,10 +1409,10 @@
       </c>
       <c r="I13" s="60">
         <f>AVERAGE(F14:H14)</f>
-        <v>3.7033333333333331</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16.5" customHeight="1">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="43"/>
       <c r="B14" s="45"/>
       <c r="C14" s="45"/>
@@ -1415,17 +1421,17 @@
         <v>15</v>
       </c>
       <c r="F14" s="11">
-        <v>3.68</v>
+        <v>3.48</v>
       </c>
       <c r="G14" s="11">
         <v>3.65</v>
       </c>
       <c r="H14" s="12">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="I14" s="61"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
         <v>29</v>
       </c>
@@ -1442,7 +1448,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>1</v>
@@ -1452,10 +1458,10 @@
       </c>
       <c r="I15" s="56">
         <f>AVERAGE(F16:H16)</f>
-        <v>7.38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="16.5" customHeight="1">
+        <v>6.5466666666666669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="37"/>
       <c r="B16" s="39"/>
       <c r="C16" s="39"/>
@@ -1464,22 +1470,22 @@
         <v>15</v>
       </c>
       <c r="F16" s="7">
-        <v>7.68</v>
+        <v>6.58</v>
       </c>
       <c r="G16" s="7">
-        <v>7.48</v>
+        <v>6.58</v>
       </c>
       <c r="H16" s="8">
-        <v>6.98</v>
+        <v>6.48</v>
       </c>
       <c r="I16" s="57"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="44" t="s">
         <v>11</v>
@@ -1491,20 +1497,20 @@
         <v>12</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I17" s="60">
         <f>AVERAGE(F18:H18)</f>
         <v>27.97</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16.5" customHeight="1">
+    <row r="18" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="43"/>
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
@@ -1523,15 +1529,15 @@
       </c>
       <c r="I18" s="61"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" s="40">
         <v>0.9</v>
@@ -1540,20 +1546,20 @@
         <v>12</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I19" s="56">
         <f>AVERAGE(F20:H20)</f>
-        <v>7.7466666666666661</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="16.5" customHeight="1">
+        <v>7.2133333333333338</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="37"/>
       <c r="B20" s="39"/>
       <c r="C20" s="39"/>
@@ -1562,22 +1568,22 @@
         <v>15</v>
       </c>
       <c r="F20" s="7">
-        <v>7.68</v>
+        <v>7.18</v>
       </c>
       <c r="G20" s="7">
-        <v>7.88</v>
+        <v>7.28</v>
       </c>
       <c r="H20" s="8">
-        <v>7.68</v>
+        <v>7.18</v>
       </c>
       <c r="I20" s="57"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="44" t="s">
         <v>11</v>
@@ -1589,20 +1595,20 @@
         <v>12</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I21" s="60">
         <f>AVERAGE(F22:H22)</f>
-        <v>45.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="16.5" customHeight="1">
+        <v>49.233333333333327</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="43"/>
       <c r="B22" s="45"/>
       <c r="C22" s="45"/>
@@ -1611,22 +1617,22 @@
         <v>15</v>
       </c>
       <c r="F22" s="11">
-        <v>47.9</v>
+        <v>53.9</v>
       </c>
       <c r="G22" s="11">
         <v>39.9</v>
       </c>
       <c r="H22" s="12">
-        <v>49.9</v>
+        <v>53.9</v>
       </c>
       <c r="I22" s="61"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>11</v>
@@ -1644,10 +1650,10 @@
       <c r="H23" s="6"/>
       <c r="I23" s="56">
         <f>AVERAGE(F24:H24)</f>
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="16.5" customHeight="1">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="37"/>
       <c r="B24" s="39"/>
       <c r="C24" s="39"/>
@@ -1656,18 +1662,18 @@
         <v>15</v>
       </c>
       <c r="F24" s="7">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="8"/>
       <c r="I24" s="57"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="42" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" s="44" t="s">
         <v>11</v>
@@ -1679,16 +1685,16 @@
         <v>12</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="10"/>
       <c r="I25" s="60">
         <f>AVERAGE(F26:H26)</f>
-        <v>2.2799999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="16.5" customHeight="1">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="43"/>
       <c r="B26" s="45"/>
       <c r="C26" s="45"/>
@@ -1697,18 +1703,18 @@
         <v>15</v>
       </c>
       <c r="F26" s="11">
-        <v>2.2799999999999998</v>
+        <v>2.7</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="12"/>
       <c r="I26" s="61"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" s="48" t="s">
         <v>11</v>
@@ -1720,16 +1726,16 @@
         <v>12</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="6"/>
       <c r="I27" s="56">
         <f>AVERAGE(F28:H28)</f>
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="16.5" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="37"/>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -1738,21 +1744,21 @@
         <v>15</v>
       </c>
       <c r="F28" s="7">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
       <c r="I28" s="57"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B29" s="44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D29" s="46">
         <v>1</v>
@@ -1761,20 +1767,20 @@
         <v>12</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I29" s="60">
         <f>AVERAGE(F30:H30)</f>
-        <v>4.4066666666666672</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="16.5" customHeight="1">
+        <v>4.4200000000000008</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="43"/>
       <c r="B30" s="52"/>
       <c r="C30" s="52"/>
@@ -1783,22 +1789,22 @@
         <v>15</v>
       </c>
       <c r="F30" s="13">
-        <v>4.38</v>
+        <v>4.68</v>
       </c>
       <c r="G30" s="13">
-        <v>4.3600000000000003</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="H30" s="14">
-        <v>4.4800000000000004</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="I30" s="61"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="36" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31" s="48" t="s">
         <v>11</v>
@@ -1810,16 +1816,16 @@
         <v>12</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="6"/>
       <c r="I31" s="56">
         <f>AVERAGE(F32:H32)</f>
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="16.5" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="37"/>
       <c r="B32" s="49"/>
       <c r="C32" s="49"/>
@@ -1828,7 +1834,7 @@
         <v>15</v>
       </c>
       <c r="F32" s="7">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="8"/>
